--- a/backtest_runs/20260410_193731/filter/DCR/DCR.xlsx
+++ b/backtest_runs/20260410_193731/filter/DCR/DCR.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-1112.799999999996</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>102225.6</v>
@@ -679,7 +679,7 @@
         <v>-6899.360000000011</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95326.24000000001</v>
@@ -771,7 +771,7 @@
         <v>-194.7400000000008</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100139.1</v>
@@ -817,7 +817,7 @@
         <v>-1530.100000000012</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>98609</v>
@@ -1185,7 +1185,7 @@
         <v>-862.4200000000063</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100278.2</v>
@@ -1231,7 +1231,7 @@
         <v>-139.0999999999921</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100139.1</v>
@@ -1277,7 +1277,7 @@
         <v>-250.3800000000095</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>99888.72</v>
@@ -1461,7 +1461,7 @@
         <v>-111.2799999999976</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>101363.18</v>
@@ -1507,7 +1507,7 @@
         <v>-556.3999999999882</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>100806.78</v>
@@ -1553,7 +1553,7 @@
         <v>-111.2800000000174</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>100695.5</v>
@@ -1645,7 +1645,7 @@
         <v>-2921.100000000012</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>100584.22</v>
